--- a/springflow_protection_presentation/data/Available Groundwater.xlsx
+++ b/springflow_protection_presentation/data/Available Groundwater.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edwardsaquifer-my.sharepoint.com/personal/eparker_edwardsaquifer_org/Documents/Desktop/Compliance Tracking/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edwardsaquifer-my.sharepoint.com/personal/cfurl_edwardsaquifer_org/Documents/SC_meetings/sep_2026/fall_meeting/EAHCP-Fall-2026-Sci-Comm/springflow_protection_presentation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="790" documentId="13_ncr:1_{6DC09DC3-0C28-4D91-8D4B-2D7BD8E7CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DE7BF62-5FE6-442E-8A7D-714736071E8F}"/>
+  <xr:revisionPtr revIDLastSave="791" documentId="13_ncr:1_{6DC09DC3-0C28-4D91-8D4B-2D7BD8E7CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80336AB9-0C24-45A0-8702-E010EB7A24C3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
@@ -1550,65 +1550,65 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2366,6 +2366,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2373,7 +2374,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3276,19 +3276,19 @@
       <c r="B1" s="61"/>
     </row>
     <row r="2" spans="2:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="194" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="197"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="196"/>
       <c r="H2"/>
-      <c r="I2" s="209" t="s">
+      <c r="I2" s="207" t="s">
         <v>53</v>
       </c>
-      <c r="J2" s="210"/>
+      <c r="J2" s="208"/>
       <c r="K2"/>
       <c r="M2" s="144" t="s">
         <v>63</v>
@@ -3298,18 +3298,18 @@
       </c>
     </row>
     <row r="3" spans="2:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="205" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="204" t="s">
+      <c r="D3" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="206"/>
-      <c r="F3" s="206"/>
-      <c r="G3" s="205"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="204"/>
       <c r="H3"/>
       <c r="I3" s="173" t="s">
         <v>45</v>
@@ -3326,7 +3326,7 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="208"/>
+      <c r="B4" s="206"/>
       <c r="C4" s="113" t="s">
         <v>22</v>
       </c>
@@ -3366,19 +3366,19 @@
         <v>23</v>
       </c>
       <c r="D5" s="44">
-        <f t="shared" ref="D5:D17" si="0">D26+H26+D47+H47</f>
+        <f>D26+H26+D47+H47</f>
         <v>571599.5</v>
       </c>
       <c r="E5" s="45">
-        <f t="shared" ref="E5:E17" si="1">E26+I26+E47+I47</f>
+        <f t="shared" ref="E5:E17" si="0">E26+I26+E47+I47</f>
         <v>564097.08000000007</v>
       </c>
       <c r="F5" s="45">
-        <f t="shared" ref="F5:F17" si="2">F26+J26+F47+J47</f>
+        <f t="shared" ref="F5:F17" si="1">F26+J26+F47+J47</f>
         <v>408178</v>
       </c>
       <c r="G5" s="46">
-        <f t="shared" ref="G5:G17" si="3">G26+K26+G47+K47</f>
+        <f t="shared" ref="G5:G17" si="2">G26+K26+G47+K47</f>
         <v>155919.08000000002</v>
       </c>
       <c r="H5" s="181"/>
@@ -3402,19 +3402,19 @@
         <v>24</v>
       </c>
       <c r="D6" s="70">
+        <f t="shared" ref="D5:D17" si="3">D27+H27+D48+H48</f>
+        <v>571599.50000000012</v>
+      </c>
+      <c r="E6" s="68">
         <f t="shared" si="0"/>
-        <v>571599.50000000012</v>
-      </c>
-      <c r="E6" s="68">
+        <v>514802.565</v>
+      </c>
+      <c r="F6" s="68">
         <f t="shared" si="1"/>
-        <v>514802.565</v>
-      </c>
-      <c r="F6" s="68">
+        <v>377255</v>
+      </c>
+      <c r="G6" s="69">
         <f t="shared" si="2"/>
-        <v>377255</v>
-      </c>
-      <c r="G6" s="69">
-        <f t="shared" si="3"/>
         <v>137547.56500000003</v>
       </c>
       <c r="H6" s="181"/>
@@ -3438,19 +3438,19 @@
         <v>25</v>
       </c>
       <c r="D7" s="52">
+        <f t="shared" si="3"/>
+        <v>571599.5</v>
+      </c>
+      <c r="E7" s="53">
         <f t="shared" si="0"/>
         <v>571599.5</v>
       </c>
-      <c r="E7" s="53">
+      <c r="F7" s="53">
         <f t="shared" si="1"/>
-        <v>571599.5</v>
-      </c>
-      <c r="F7" s="53">
+        <v>354081</v>
+      </c>
+      <c r="G7" s="54">
         <f t="shared" si="2"/>
-        <v>354081</v>
-      </c>
-      <c r="G7" s="54">
-        <f t="shared" si="3"/>
         <v>217518.5</v>
       </c>
       <c r="H7" s="181"/>
@@ -3474,19 +3474,19 @@
         <v>26</v>
       </c>
       <c r="D8" s="70">
+        <f t="shared" si="3"/>
+        <v>571599.5</v>
+      </c>
+      <c r="E8" s="68">
         <f t="shared" si="0"/>
-        <v>571599.5</v>
-      </c>
-      <c r="E8" s="68">
+        <v>476851.81600000005</v>
+      </c>
+      <c r="F8" s="68">
         <f t="shared" si="1"/>
-        <v>476851.81600000005</v>
-      </c>
-      <c r="F8" s="68">
+        <v>408628</v>
+      </c>
+      <c r="G8" s="69">
         <f t="shared" si="2"/>
-        <v>408628</v>
-      </c>
-      <c r="G8" s="69">
-        <f t="shared" si="3"/>
         <v>68223.816000000006</v>
       </c>
       <c r="H8" s="181"/>
@@ -3510,19 +3510,19 @@
         <v>27</v>
       </c>
       <c r="D9" s="52">
+        <f t="shared" si="3"/>
+        <v>571599.50000000012</v>
+      </c>
+      <c r="E9" s="53">
         <f t="shared" si="0"/>
-        <v>571599.50000000012</v>
-      </c>
-      <c r="E9" s="53">
+        <v>448136.40099999995</v>
+      </c>
+      <c r="F9" s="53">
         <f t="shared" si="1"/>
-        <v>448136.40099999995</v>
-      </c>
-      <c r="F9" s="53">
+        <v>370993</v>
+      </c>
+      <c r="G9" s="54">
         <f t="shared" si="2"/>
-        <v>370993</v>
-      </c>
-      <c r="G9" s="54">
-        <f t="shared" si="3"/>
         <v>77143.400999999983</v>
       </c>
       <c r="H9" s="181"/>
@@ -3546,19 +3546,19 @@
         <v>28</v>
       </c>
       <c r="D10" s="70">
+        <f t="shared" si="3"/>
+        <v>571599.5</v>
+      </c>
+      <c r="E10" s="68">
         <f t="shared" si="0"/>
-        <v>571599.5</v>
-      </c>
-      <c r="E10" s="68">
+        <v>394826.10700000002</v>
+      </c>
+      <c r="F10" s="68">
         <f t="shared" si="1"/>
-        <v>394826.10700000002</v>
-      </c>
-      <c r="F10" s="68">
+        <v>336634</v>
+      </c>
+      <c r="G10" s="69">
         <f t="shared" si="2"/>
-        <v>336634</v>
-      </c>
-      <c r="G10" s="69">
-        <f t="shared" si="3"/>
         <v>58192.107000000025</v>
       </c>
       <c r="H10" s="181"/>
@@ -3582,19 +3582,19 @@
         <v>29</v>
       </c>
       <c r="D11" s="52">
+        <f t="shared" si="3"/>
+        <v>571599.5</v>
+      </c>
+      <c r="E11" s="53">
         <f t="shared" si="0"/>
-        <v>571599.5</v>
-      </c>
-      <c r="E11" s="53">
+        <v>363534.97</v>
+      </c>
+      <c r="F11" s="53">
         <f t="shared" si="1"/>
-        <v>363534.97</v>
-      </c>
-      <c r="F11" s="53">
+        <v>312948.61200000002</v>
+      </c>
+      <c r="G11" s="54">
         <f t="shared" si="2"/>
-        <v>312948.61200000002</v>
-      </c>
-      <c r="G11" s="54">
-        <f t="shared" si="3"/>
         <v>50586.357999999993</v>
       </c>
       <c r="H11" s="181"/>
@@ -3618,7 +3618,7 @@
         <v>33</v>
       </c>
       <c r="D12" s="70">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>571599.5</v>
       </c>
       <c r="E12" s="68">
@@ -3626,11 +3626,11 @@
         <v>425788.34100000001</v>
       </c>
       <c r="F12" s="68">
+        <f t="shared" si="1"/>
+        <v>305507.35800000007</v>
+      </c>
+      <c r="G12" s="69">
         <f t="shared" si="2"/>
-        <v>305507.35800000007</v>
-      </c>
-      <c r="G12" s="69">
-        <f t="shared" si="3"/>
         <v>120280.98299999993</v>
       </c>
       <c r="H12" s="181"/>
@@ -3655,19 +3655,19 @@
         <v>25</v>
       </c>
       <c r="D13" s="52">
+        <f t="shared" si="3"/>
+        <v>571599.5</v>
+      </c>
+      <c r="E13" s="53">
         <f t="shared" si="0"/>
         <v>571599.5</v>
       </c>
-      <c r="E13" s="53">
+      <c r="F13" s="53">
         <f t="shared" si="1"/>
-        <v>571599.5</v>
-      </c>
-      <c r="F13" s="53">
+        <v>305994.09499999997</v>
+      </c>
+      <c r="G13" s="54">
         <f t="shared" si="2"/>
-        <v>305994.09499999997</v>
-      </c>
-      <c r="G13" s="54">
-        <f t="shared" si="3"/>
         <v>265605.40500000003</v>
       </c>
       <c r="H13" s="181"/>
@@ -3693,19 +3693,19 @@
         <v>48</v>
       </c>
       <c r="D14" s="70">
+        <f t="shared" si="3"/>
+        <v>571599</v>
+      </c>
+      <c r="E14" s="68">
         <f t="shared" si="0"/>
-        <v>571599</v>
-      </c>
-      <c r="E14" s="68">
+        <v>555471.70400000003</v>
+      </c>
+      <c r="F14" s="68">
         <f t="shared" si="1"/>
-        <v>555471.70400000003</v>
-      </c>
-      <c r="F14" s="68">
+        <v>359851.97200000001</v>
+      </c>
+      <c r="G14" s="69">
         <f t="shared" si="2"/>
-        <v>359851.97200000001</v>
-      </c>
-      <c r="G14" s="69">
-        <f t="shared" si="3"/>
         <v>195619.73200000008</v>
       </c>
       <c r="H14" s="181"/>
@@ -3729,19 +3729,19 @@
         <v>49</v>
       </c>
       <c r="D15" s="52">
+        <f t="shared" si="3"/>
+        <v>571599</v>
+      </c>
+      <c r="E15" s="53">
         <f t="shared" si="0"/>
-        <v>571599</v>
-      </c>
-      <c r="E15" s="53">
+        <v>531073</v>
+      </c>
+      <c r="F15" s="53">
         <f t="shared" si="1"/>
-        <v>531073</v>
-      </c>
-      <c r="F15" s="53">
+        <v>351140</v>
+      </c>
+      <c r="G15" s="54">
         <f t="shared" si="2"/>
-        <v>351140</v>
-      </c>
-      <c r="G15" s="54">
-        <f t="shared" si="3"/>
         <v>179933</v>
       </c>
       <c r="H15" s="181"/>
@@ -3765,19 +3765,19 @@
         <v>25</v>
       </c>
       <c r="D16" s="70">
+        <f t="shared" si="3"/>
+        <v>571599.5</v>
+      </c>
+      <c r="E16" s="68">
         <f t="shared" si="0"/>
         <v>571599.5</v>
       </c>
-      <c r="E16" s="68">
+      <c r="F16" s="68">
         <f t="shared" si="1"/>
-        <v>571599.5</v>
-      </c>
-      <c r="F16" s="68">
+        <v>339019.63499999995</v>
+      </c>
+      <c r="G16" s="69">
         <f t="shared" si="2"/>
-        <v>339019.63499999995</v>
-      </c>
-      <c r="G16" s="69">
-        <f t="shared" si="3"/>
         <v>232579.86500000005</v>
       </c>
       <c r="H16" s="181"/>
@@ -3801,19 +3801,19 @@
         <v>61</v>
       </c>
       <c r="D17" s="176">
+        <f t="shared" si="3"/>
+        <v>571599.5</v>
+      </c>
+      <c r="E17" s="177">
         <f t="shared" si="0"/>
-        <v>571599.5</v>
-      </c>
-      <c r="E17" s="177">
+        <v>541805.24800000002</v>
+      </c>
+      <c r="F17" s="177">
         <f t="shared" si="1"/>
-        <v>541805.24800000002</v>
-      </c>
-      <c r="F17" s="177">
+        <v>342457.27299999993</v>
+      </c>
+      <c r="G17" s="178">
         <f t="shared" si="2"/>
-        <v>342457.27299999993</v>
-      </c>
-      <c r="G17" s="178">
-        <f t="shared" si="3"/>
         <v>199347.97500000003</v>
       </c>
       <c r="H17" s="181"/>
@@ -3953,38 +3953,38 @@
       <c r="F22" s="120"/>
     </row>
     <row r="23" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="198" t="s">
+      <c r="B23" s="191" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="199"/>
-      <c r="D23" s="199"/>
-      <c r="E23" s="199"/>
-      <c r="F23" s="199"/>
-      <c r="G23" s="199"/>
-      <c r="H23" s="199"/>
-      <c r="I23" s="199"/>
-      <c r="J23" s="199"/>
-      <c r="K23" s="200"/>
+      <c r="C23" s="192"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="192"/>
+      <c r="F23" s="192"/>
+      <c r="G23" s="192"/>
+      <c r="H23" s="192"/>
+      <c r="I23" s="192"/>
+      <c r="J23" s="192"/>
+      <c r="K23" s="193"/>
     </row>
     <row r="24" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="193" t="s">
+      <c r="B24" s="197" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="193" t="s">
+      <c r="C24" s="197" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="201" t="s">
+      <c r="D24" s="199" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="191"/>
-      <c r="F24" s="191"/>
-      <c r="G24" s="192"/>
-      <c r="H24" s="191" t="s">
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="201"/>
+      <c r="H24" s="200" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="191"/>
-      <c r="J24" s="191"/>
-      <c r="K24" s="192"/>
+      <c r="I24" s="200"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="201"/>
       <c r="M24" s="188" t="s">
         <v>31</v>
       </c>
@@ -3992,8 +3992,8 @@
       <c r="O24" s="190"/>
     </row>
     <row r="25" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="194"/>
-      <c r="C25" s="194"/>
+      <c r="B25" s="198"/>
+      <c r="C25" s="198"/>
       <c r="D25" s="39" t="s">
         <v>17</v>
       </c>
@@ -4910,38 +4910,38 @@
     </row>
     <row r="43" spans="2:18" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="44" spans="2:18" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="198" t="s">
+      <c r="B44" s="191" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="199"/>
-      <c r="D44" s="199"/>
-      <c r="E44" s="199"/>
-      <c r="F44" s="199"/>
-      <c r="G44" s="199"/>
-      <c r="H44" s="199"/>
-      <c r="I44" s="199"/>
-      <c r="J44" s="199"/>
-      <c r="K44" s="200"/>
+      <c r="C44" s="192"/>
+      <c r="D44" s="192"/>
+      <c r="E44" s="192"/>
+      <c r="F44" s="192"/>
+      <c r="G44" s="192"/>
+      <c r="H44" s="192"/>
+      <c r="I44" s="192"/>
+      <c r="J44" s="192"/>
+      <c r="K44" s="193"/>
     </row>
     <row r="45" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="193" t="s">
+      <c r="B45" s="197" t="s">
         <v>0</v>
       </c>
-      <c r="C45" s="193" t="s">
+      <c r="C45" s="197" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="201" t="s">
+      <c r="D45" s="199" t="s">
         <v>18</v>
       </c>
-      <c r="E45" s="191"/>
-      <c r="F45" s="191"/>
-      <c r="G45" s="192"/>
-      <c r="H45" s="191" t="s">
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="201"/>
+      <c r="H45" s="200" t="s">
         <v>19</v>
       </c>
-      <c r="I45" s="191"/>
-      <c r="J45" s="191"/>
-      <c r="K45" s="192"/>
+      <c r="I45" s="200"/>
+      <c r="J45" s="200"/>
+      <c r="K45" s="201"/>
       <c r="L45" s="48"/>
       <c r="M45" s="188" t="s">
         <v>32</v>
@@ -4950,8 +4950,8 @@
       <c r="O45" s="190"/>
     </row>
     <row r="46" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="194"/>
-      <c r="C46" s="194"/>
+      <c r="B46" s="198"/>
+      <c r="C46" s="198"/>
       <c r="D46" s="39" t="s">
         <v>17</v>
       </c>
@@ -5909,36 +5909,36 @@
       <c r="B64" s="61"/>
     </row>
     <row r="65" spans="2:18" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="198" t="s">
+      <c r="B65" s="191" t="s">
         <v>43</v>
       </c>
-      <c r="C65" s="199"/>
-      <c r="D65" s="199"/>
-      <c r="E65" s="199"/>
-      <c r="F65" s="199"/>
-      <c r="G65" s="199"/>
-      <c r="H65" s="199"/>
-      <c r="I65" s="199"/>
-      <c r="J65" s="199"/>
-      <c r="K65" s="200"/>
+      <c r="C65" s="192"/>
+      <c r="D65" s="192"/>
+      <c r="E65" s="192"/>
+      <c r="F65" s="192"/>
+      <c r="G65" s="192"/>
+      <c r="H65" s="192"/>
+      <c r="I65" s="192"/>
+      <c r="J65" s="192"/>
+      <c r="K65" s="193"/>
     </row>
     <row r="66" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="202" t="s">
+      <c r="B66" s="209" t="s">
         <v>0</v>
       </c>
-      <c r="C66" s="203"/>
-      <c r="D66" s="201" t="s">
+      <c r="C66" s="210"/>
+      <c r="D66" s="199" t="s">
         <v>18</v>
       </c>
-      <c r="E66" s="191"/>
-      <c r="F66" s="191"/>
-      <c r="G66" s="192"/>
-      <c r="H66" s="191" t="s">
+      <c r="E66" s="200"/>
+      <c r="F66" s="200"/>
+      <c r="G66" s="201"/>
+      <c r="H66" s="200" t="s">
         <v>19</v>
       </c>
-      <c r="I66" s="191"/>
-      <c r="J66" s="191"/>
-      <c r="K66" s="192"/>
+      <c r="I66" s="200"/>
+      <c r="J66" s="200"/>
+      <c r="K66" s="201"/>
       <c r="L66" s="48"/>
       <c r="M66" s="188" t="s">
         <v>44</v>
@@ -5947,8 +5947,8 @@
       <c r="O66" s="190"/>
     </row>
     <row r="67" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="204"/>
-      <c r="C67" s="205"/>
+      <c r="B67" s="202"/>
+      <c r="C67" s="204"/>
       <c r="D67" s="39" t="s">
         <v>17</v>
       </c>
@@ -6909,41 +6909,41 @@
       <c r="O85" s="62"/>
     </row>
     <row r="86" spans="2:18" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="198" t="s">
+      <c r="B86" s="191" t="s">
         <v>43</v>
       </c>
-      <c r="C86" s="199"/>
-      <c r="D86" s="199"/>
-      <c r="E86" s="199"/>
-      <c r="F86" s="199"/>
-      <c r="G86" s="199"/>
-      <c r="H86" s="199"/>
-      <c r="I86" s="199"/>
-      <c r="J86" s="199"/>
-      <c r="K86" s="200"/>
+      <c r="C86" s="192"/>
+      <c r="D86" s="192"/>
+      <c r="E86" s="192"/>
+      <c r="F86" s="192"/>
+      <c r="G86" s="192"/>
+      <c r="H86" s="192"/>
+      <c r="I86" s="192"/>
+      <c r="J86" s="192"/>
+      <c r="K86" s="193"/>
       <c r="M86" s="62"/>
       <c r="N86" s="62"/>
       <c r="O86" s="62"/>
     </row>
     <row r="87" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="193" t="s">
+      <c r="B87" s="197" t="s">
         <v>0</v>
       </c>
-      <c r="C87" s="193" t="s">
+      <c r="C87" s="197" t="s">
         <v>21</v>
       </c>
-      <c r="D87" s="201" t="s">
+      <c r="D87" s="199" t="s">
         <v>31</v>
       </c>
-      <c r="E87" s="191"/>
-      <c r="F87" s="191"/>
-      <c r="G87" s="192"/>
-      <c r="H87" s="191" t="s">
+      <c r="E87" s="200"/>
+      <c r="F87" s="200"/>
+      <c r="G87" s="201"/>
+      <c r="H87" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="I87" s="191"/>
-      <c r="J87" s="191"/>
-      <c r="K87" s="192"/>
+      <c r="I87" s="200"/>
+      <c r="J87" s="200"/>
+      <c r="K87" s="201"/>
       <c r="L87" s="48"/>
       <c r="M87" s="188" t="s">
         <v>44</v>
@@ -6952,8 +6952,8 @@
       <c r="O87" s="190"/>
     </row>
     <row r="88" spans="2:18" s="38" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="194"/>
-      <c r="C88" s="194"/>
+      <c r="B88" s="198"/>
+      <c r="C88" s="198"/>
       <c r="D88" s="39" t="s">
         <v>17</v>
       </c>
@@ -7903,12 +7903,12 @@
       <c r="I106" s="66"/>
     </row>
     <row r="107" spans="2:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="195" t="s">
+      <c r="B107" s="194" t="s">
         <v>54</v>
       </c>
-      <c r="C107" s="196"/>
-      <c r="D107" s="196"/>
-      <c r="E107" s="197"/>
+      <c r="C107" s="195"/>
+      <c r="D107" s="195"/>
+      <c r="E107" s="196"/>
       <c r="F107" s="66"/>
       <c r="G107" s="66"/>
     </row>
@@ -8094,6 +8094,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B65:K65"/>
+    <mergeCell ref="D66:G66"/>
+    <mergeCell ref="H66:K66"/>
+    <mergeCell ref="B66:C67"/>
     <mergeCell ref="M66:O66"/>
     <mergeCell ref="B23:K23"/>
     <mergeCell ref="B2:G2"/>
@@ -8110,18 +8122,6 @@
     <mergeCell ref="M87:O87"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="D45:G45"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B65:K65"/>
-    <mergeCell ref="D66:G66"/>
-    <mergeCell ref="H66:K66"/>
-    <mergeCell ref="B66:C67"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
@@ -15579,15 +15579,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C603F341640631408A2643E393A60B53" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e0bfc2e3fc1aada3540c7000aa650a01">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4b8598d9-10f0-4e4a-b724-2bdbbdf39591" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="916044e20d8ff787e60ff4acb6d8aa77" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -15758,6 +15749,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53011E8F-F684-4283-82B5-1DB773207276}">
   <ds:schemaRefs>
@@ -15776,14 +15776,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C23834BE-FF54-40F7-94EE-EDEF8EF82749}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2147AFE-63F4-4B3E-A1B4-F1EBE737CC2B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15800,4 +15792,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C23834BE-FF54-40F7-94EE-EDEF8EF82749}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>